--- a/backend/product-upload-one.xlsx
+++ b/backend/product-upload-one.xlsx
@@ -1,65 +1,150 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet r:id="rId1" name="Products" sheetId="1"/>
+    <sheet r:id="rId2" name="How to use" sheetId="2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>slug</t>
+  </si>
+  <si>
+    <t>sku</t>
+  </si>
+  <si>
+    <t>shortDescription</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>discountPrice</t>
+  </si>
+  <si>
+    <t>stock</t>
+  </si>
+  <si>
+    <t>images</t>
+  </si>
+  <si>
+    <t>Lenovo IdeaPad Gaming 3</t>
+  </si>
+  <si>
+    <t>15.6 inch gaming laptop</t>
+  </si>
+  <si>
+    <t>Ryzen 5, 16GB RAM, 512GB SSD, RTX 3050</t>
+  </si>
+  <si>
+    <t>Sample Product Two</t>
+  </si>
+  <si>
+    <t>Everyday laptop</t>
+  </si>
+  <si>
+    <t>Core i3, 8GB RAM, 256GB SSD</t>
+  </si>
+  <si>
+    <t>uploads/example-one.jpg, uploads/example-two.jpg</t>
+  </si>
+  <si>
+    <t>Product upload sheet: how to use</t>
+  </si>
+  <si>
+    <t>1. Keep row 1 (the header) exactly as it is. Header names are case-sensitive: title, slug, sku, shortDescription, description, price, discountPrice, stock, images.</t>
+  </si>
+  <si>
+    <t>2. Write one product per row in the first sheet ("Products"). A column may be left out, a cell may be empty.</t>
+  </si>
+  <si>
+    <t>3. Yellow cells (title) must be new for every upload: a title or slug that already exists makes the upload fail.</t>
+  </si>
+  <si>
+    <t>4. slug and sku can stay empty, they are generated automatically.</t>
+  </si>
+  <si>
+    <t>5. images: optional, existing image paths separated by commas. The first one becomes the main image.</t>
+  </si>
+  <si>
+    <t>6. Every uploaded product gets the default category and subcategory written at the top of bulkuploadProductsExcelController (productControllers.js).</t>
+  </si>
+  <si>
+    <t>7. Upload with POST /api/v1/vendor/products/bulk-upload (form-data, key: file, type: File).</t>
+  </si>
+  <si>
+    <t>Rows 2 and 3 of the Products sheet are example rows: change the titles or delete them before a real upload.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <i val="0"/>
+      <sz val="10"/>
+      <color auto="1"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <sz val="10"/>
+      <color auto="1"/>
       <name val="Arial"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
+      <color auto="1"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDE8F5"/>
+        <fgColor rgb="FFDDE8F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -69,108 +154,79 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B9C9DE"/>
+        <color rgb="FFB9C9DE"/>
       </left>
       <right style="thin">
-        <color rgb="00B9C9DE"/>
+        <color rgb="FFB9C9DE"/>
       </right>
       <top style="thin">
-        <color rgb="00B9C9DE"/>
+        <color rgb="FFB9C9DE"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B9C9DE"/>
+        <color rgb="FFB9C9DE"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB9C9DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB9C9DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB9C9DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB9C9DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" quotePrefix="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" quotePrefix="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+  <bag type="DXFComplements" extRef="DXFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -219,10 +275,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="&amp;#xFF2D;&amp;#xFF33; &amp;#xFF30;&amp;#x30B4;&amp;#x30B7;&amp;#x30C3;&amp;#x30AF;"/>
+        <a:font script="Hang" typeface="&amp;#xB9D1;&amp;#xC740; &amp;#xACE0;&amp;#xB515;"/>
+        <a:font script="Hans" typeface="&amp;#x5B8B;&amp;#x4F53;"/>
+        <a:font script="Hant" typeface="&amp;#x65B0;&amp;#x7D30;&amp;#x660E;&amp;#x9AD4;"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -253,10 +309,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="&amp;#xFF2D;&amp;#xFF33; &amp;#xFF30;&amp;#x30B4;&amp;#x30B7;&amp;#x30C3;&amp;#x30AF;"/>
+        <a:font script="Hang" typeface="&amp;#xB9D1;&amp;#xC740; &amp;#xACE0;&amp;#xB515;"/>
+        <a:font script="Hans" typeface="&amp;#x5B8B;&amp;#x4F53;"/>
+        <a:font script="Hant" typeface="&amp;#x65B0;&amp;#x7D30;&amp;#x660E;&amp;#x9AD4;"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -457,221 +513,177 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{2164EE61-DA3D-4B47-9C29-CCD4DFD3FA47}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
+    <col min="1" max="1" width="30.00390625" customWidth="1"/>
+    <col min="2" max="2" width="18.00390625" customWidth="1"/>
+    <col min="3" max="3" width="14.00390625" customWidth="1"/>
+    <col min="4" max="4" width="28.00390625" customWidth="1"/>
+    <col min="5" max="5" width="42.00390625" customWidth="1"/>
+    <col min="6" max="6" width="10.00390625" customWidth="1"/>
+    <col min="7" max="7" width="14.00390625" customWidth="1"/>
+    <col min="8" max="8" width="8.00390625" customWidth="1"/>
+    <col min="9" max="9" width="48.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>slug</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sku</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>shortDescription</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>discountPrice</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>images</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Lenovo IdeaPad Gaming 3</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>15.6 inch gaming laptop</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Ryzen 5, 16GB RAM, 512GB SSD, RTX 3050</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3">
         <v>85000</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="3">
         <v>80000</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="3">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Sample Product Two</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Everyday laptop</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Core i3, 8GB RAM, 256GB SSD</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3">
         <v>45000</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="3">
         <v>0</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="3">
         <v>15</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>uploads/example-one.jpg, uploads/example-two.jpg</t>
-        </is>
+      <c r="I3" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <printOptions/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  </headerFooter>
+  <extLst/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{BA5EB795-B58D-42F7-B2B5-9120EEC65748}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col width="140" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="140.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Product upload sheet: how to use</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>1. Keep row 1 (the header) exactly as it is. Header names are case-sensitive: title, slug, sku, shortDescription, description, price, discountPrice, stock, images.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>2. Write one product per row in the first sheet ("Products"). A column may be left out, a cell may be empty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>3. Yellow cells (title) must be new for every upload: a title or slug that already exists makes the upload fail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>4. slug and sku can stay empty, they are generated automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>5. images: optional, existing image paths separated by commas. The first one becomes the main image.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>6. Every uploaded product gets the default category and subcategory written at the top of bulkuploadProductsExcelController (productControllers.js).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>7. Upload with POST /api/v1/vendor/products/bulk-upload (form-data, key: file, type: File).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Rows 2 and 3 of the Products sheet are example rows: change the titles or delete them before a real upload.</t>
-        </is>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="5"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="5"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
+  <printOptions/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  </headerFooter>
+  <extLst/>
 </worksheet>
 </file>